--- a/data/trans_orig/IP07KS_C09_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C09_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de ir bien en el colegio en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de ir bien en el colegio, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20185</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14861</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25940</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,62%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>37,26%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>65,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19965</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15513</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24036</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>65,49%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>50,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19823</t>
+          <t>20919</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14339</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>25038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,17 +795,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>39788</t>
+          <t>41103</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32631</t>
+          <t>33049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47012</t>
+          <t>48175</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>66,99%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18711</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13027</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24085</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>60,4%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9734</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14343</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>31,93%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19,48%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18227</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23842</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>27961</t>
+          <t>28963</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21310</t>
+          <t>21861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35867</t>
+          <t>36951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,39%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3577</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,97%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4685</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,37%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3995</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>447</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20416</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15138</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25446</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>61,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>76,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9769</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6079</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14710</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33,49%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19795</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25011</t>
+          <t>15420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29564</t>
+          <t>30822</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22219</t>
+          <t>23874</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36369</t>
+          <t>38410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>60,05%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10343</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6426</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15708</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>17716</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>13145</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21932</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>60,74%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>45,07%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>75,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>18542</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>13622</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15348</t>
+          <t>23148</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>28885</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35368</t>
+          <t>35930</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>56,17%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2436</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6705</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20,2%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2762</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3139</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2451</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6426</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>867</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -1854,107 +1854,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6101</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4924</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,92%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5084</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6090</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12831</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7976</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18041</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>47,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>66,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4907</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2193</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8167</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33,73%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,07%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13170</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18810</t>
+          <t>9193</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>18270</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>12998</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>25021</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,82%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9092</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5111</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14092</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>52,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>8171</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8550</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>5042</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>11017</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>56,16%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>9176</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>4836</t>
-        </is>
-      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>11874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>17348</t>
+          <t>17642</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>23422</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,06%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3447</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7860</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,78%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>29,14%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1471</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4665</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1578</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4637</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>32,06%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3646</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>8540</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -2423,107 +2423,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5647</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>20,94%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1693</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5145</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1603</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5556</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>18,58%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1693</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5635</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>30913</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>21508</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>40736</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>44,96%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>31,29%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>59,25%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>4561</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>26521</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>21,56%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>39,49%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>30736</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20985</t>
+          <t>9491</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41082</t>
+          <t>20642</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>45211</t>
+          <t>45892</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>35663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62999</t>
+          <t>57990</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>51,61%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>21865</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>14338</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>30428</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>31,8%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>20,86%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>44,26%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>18430</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>5675</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>33978</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>27,44%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>50,6%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>22368</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>13144</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31155</t>
+          <t>24340</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>40799</t>
+          <t>40312</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22628</t>
+          <t>29848</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56008</t>
+          <t>49847</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>13622</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5256</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>27135</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>19,81%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>39,47%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>33273</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>8772</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>55425</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>49,55%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>13,06%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>82,53%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>4898</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29331</t>
+          <t>17223</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>47559</t>
+          <t>22849</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21581</t>
+          <t>13072</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>88712</t>
+          <t>38616</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8672</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>12,61%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3688</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3146</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2646</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>10976</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -3218,107 +3218,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>2422</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>68749</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>68749</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>68749</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70037</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70037</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70037</t>
+          <t>43616</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>137192</t>
+          <t>112365</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>137192</t>
+          <t>112365</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137192</t>
+          <t>112365</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>35755</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>27070</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>46326</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>60,46%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>45,77%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>20177</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>14939</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>24817</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>56,5%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>41,83%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>69,5%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>37211</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28489</t>
+          <t>16496</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48255</t>
+          <t>27468</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>57388</t>
+          <t>57780</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>47058</t>
+          <t>48161</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>70186</t>
+          <t>68985</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>11513</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>6191</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>18405</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>19,47%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>10,47%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>31,12%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>13811</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>9281</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>19389</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>38,68%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>25,99%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>54,3%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>20406</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>25069</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>18724</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34242</t>
+          <t>35771</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>9097</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>4066</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>16235</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>15,38%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>6,88%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>27,45%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>3985</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3959</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>9477</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>4165</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>16502</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>15,59%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18676</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>7487</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>12,66%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>2681</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3160</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>2238</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>7123</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2722</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>2943</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>2735</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>16032</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>10333</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>21835</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>43,9%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>28,29%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>59,79%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>18495</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>14050</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>22867</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>61,29%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>46,56%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>75,78%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>15702</t>
+          <t>20438</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10266</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20932</t>
+          <t>25002</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>34196</t>
+          <t>36470</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>27359</t>
+          <t>28694</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>40999</t>
+          <t>43609</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,61%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>17950</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>12093</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>24137</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>49,15%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>33,11%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>66,09%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>7879</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>4375</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>12303</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>26,11%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>40,77%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12886</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23589</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>25699</t>
+          <t>26710</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>19646</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32559</t>
+          <t>33946</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>1642</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>5332</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>14,6%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>2859</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>6071</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>20,12%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>916</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>4274</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>11,7%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>3316</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3343</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>10,99%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>4393</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>363</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>136132</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>119057</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>155907</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>51,48%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>45,02%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>58,95%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>87788</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>55010</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>107484</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>42,36%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>26,54%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>51,86%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>136437</t>
+          <t>94206</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>118517</t>
+          <t>81964</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>155834</t>
+          <t>105925</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>224224</t>
+          <t>230337</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>181044</t>
+          <t>208948</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>250324</t>
+          <t>253133</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>89476</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>74190</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>105683</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>33,83%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>28,05%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>39,96%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>75742</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>50660</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>93276</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>36,55%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>45,01%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>89043</t>
+          <t>79657</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>72562</t>
+          <t>67990</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>103373</t>
+          <t>91955</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>164784</t>
+          <t>169133</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>133823</t>
+          <t>149102</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>190316</t>
+          <t>189349</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>41,29%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>31227</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>21402</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>49208</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>11,81%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>18,61%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>40113</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>13037</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>109946</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>53,05%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>32617</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>52343</t>
+          <t>26306</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>72730</t>
+          <t>47714</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>42678</t>
+          <t>34751</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>156822</t>
+          <t>68571</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>3449</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>14639</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>4883</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>14485</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>18120</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2972</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>1576</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>6414</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>1594</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>8149</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>3606</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>366</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>264460</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>264460</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>264460</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>207246</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>266133</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>266133</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>266133</t>
+          <t>194089</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>473378</t>
+          <t>458549</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>473378</t>
+          <t>458549</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>473378</t>
+          <t>458549</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
